--- a/RPTToSpreadsheet/Test Resources/Output/MATOPT (1)(1).xlsx
+++ b/RPTToSpreadsheet/Test Resources/Output/MATOPT (1)(1).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t>ControlName</t>
   </si>
@@ -28,6 +28,1631 @@
   </si>
   <si>
     <t>Script</t>
+  </si>
+  <si>
+    <t>MAIN FORM CONTROL</t>
+  </si>
+  <si>
+    <t>MATOPT</t>
+  </si>
+  <si>
+    <t>Matter Format Options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public gstrClientCode As String
+Public gstrClientName As String
+Public gstrMatterCode As String
+Public gstrMatterName As String
+Public gstrCmdExe As String
+Public gstrCmdParm1 As String
+Public gstrBillMUno As String
+Public gbAccessDiscount As Boolean
+Function FindSelectedListItem(ByVal hList As List, ByVal strSearchItem As String, ByVal strColumnTitle As String) As Integer
+  Dim nLoop As Integer
+  Dim nFoundLocation As Integer
+  Dim strSelectedItem As String
+  ' Initialise variables.
+  nFoundLocation = 0
+  ' Loop through list items.
+  For nLoop = 1 To hList.Count
+    ' Determine if current item is selected.
+    If hList.Selected(nLoop) Then
+      ' Obtain value of selected row in the specified column.
+      strSelectedItem = ""
+      strSelectedItem = Trim$(hList.RowItem(nLoop, hList.FindColumn(strColumnTitle)))
+      ' Determine if selected item is same as the search item.
+      If strSelectedItem = strSearchItem Then
+        ' Match found, hold the row.
+        nFoundLocation = nLoop
+        ' Stop further processing.
+        Exit For
+      End If  ' Match Check
+    End If ' Selected Row Check
+  Next nLoop
+  ' Return value.
+  FindSelectedListItem = nFoundLocation  
+End Function
+Function FindListItem(ByVal hList As List, ByVal strSearchItem As String, ByVal strColumnTitle As String) As Integer
+  Dim nLoop As Integer
+  Dim nFoundLocation As Integer
+  Dim strSelectedItem As String
+  ' Initialise variables.
+  nFoundLocation = 0
+  ' Loop through list items.
+  For nLoop = 1 To hList.Count
+    ' Obtain value of selected row in the specified column.
+    strSelectedItem = ""
+    strSelectedItem = Trim$(hList.RowItem(nLoop, hList.FindColumn(strColumnTitle)))
+    ' Determine if selected item is same as the search item.
+    If strSelectedItem = strSearchItem Then
+      ' Match found, hold the row.
+      nFoundLocation = nLoop
+      ' Stop further processing.
+      Exit For
+    End If  ' Match Check
+  Next nLoop
+  ' Return value.
+  FindListItem = nFoundLocation  
+End Function
+Function MakeIncludeString(ByVal hList As List, ByVal strArea As String) As String
+  Const sDELIMITER_COMMA As String = ","
+  Const sSECTION_TIME_SUMMARY As String = "TS"
+  Const sSECTION_TIME_DETAIL As String = "TD"
+  Const sSECTION_DISB_SUMMARY As String = "DS"
+  Const sSECTION_DISB_DETAIL As String = "DD"
+  Const sSECTION_DISB_DETAIL_DISB_ONLY As String = "DDDI"
+  Const sCOLUMN_TITLE_ROW_UNO As String = "Row Uno"
+  Const sCOLUMN_TITLE_DD_NAME As String = "DD Name"
+  Const sCOLUMN_TITLE_TIME_FIELD As String = "Time Field"
+  Const sCOLUMN_TITLE_DISB_FIELD As String = "Disbursement Field"
+  Const sCOLUMN_TITLE_DISB_CODE As String = "Disbursement Type"
+  Const sCOLUMN_TITLE_DESCRIPTION As String = "Description"
+  Const sCOLUMN_TITLE_MIN_SIZE As String = "Min Size"
+  Const sCOLUMN_TITLE_MAX_SIZE As String = "Max Size"
+  Dim nRows As Long
+  Dim nLoop As Long
+  Dim strRowUno As String
+  Dim strDDName As String
+  Dim strField As String
+  Dim strDesc As String
+  DIm strMinSize As String
+  Dim strMaxSize As String
+  Dim strData As String
+  ' Obtain number of rows in source list. 
+  nRows = hList.Count
+  strData = ""
+  ' Determine if there are rows in the list.
+  If nRows &gt; 0 Then
+    ' Loop through list.
+    For nLoop = 1 To nRows
+      ' Determine if using disbursement detail disbursement code list.
+      If strArea &lt;&gt; sSECTION_DISB_DETAIL_DISB_ONLY Then
+        ' Not disbursement code list.
+        ' Obtain information from selected row.
+        strRowUno = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_ROW_UNO))
+        strDDName = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_DD_NAME))
+        ' Determine the section area.
+        Select Case strArea
+          Case sSECTION_TIME_SUMMARY, sSECTION_TIME_DETAIL
+            strField = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_TIME_FIELD))
+          Case sSECTION_DISB_SUMMARY, sSECTION_DISB_DETAIL
+            strField = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_DISB_FIELD))
+        End Select
+        strDesc = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_DESCRIPTION))
+        strMinSize = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_MIN_SIZE))
+        strMaxSize = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_MAX_SIZE))
+        ' Build row data.
+        strData = strData + strDDName + sDELIMITER_COMMA
+      Else
+        ' Disbursement code list.
+        strDDName = hList.RowItem(nLoop, hList.FindColumn(sCOLUMN_TITLE_DISB_CODE))
+        ' Build row data.
+        strData = strData + strDDName + sDELIMITER_COMMA
+      End If
+    Next nLoop
+    ' Remove trailing delimiter.
+    strData = Left$(strData, Len(strData) - 1)
+  End If ' Row Check.
+  ' Return data.
+  MakeIncludeString = strData
+End Function
+Function MakeMultiString(ByVal strCode As String, ByVal strDelimiter As String, ByVal strEnclosedChar As String) As String
+  Dim nPos As Integer
+  Dim nStart As Integer
+  Dim strTemp As String
+  ' Initialise variables.
+  nPos = 0
+  strTemp = ""
+  strCode = Trim$(strCode)
+  ' Find initial position of delimiter.
+  nPos = InStr(strCode, strDelimiter)
+  ' Determine if find initial delimiter.
+  If nPos = 0 Then
+    ' Single item already selected.
+    strTemp = strEnclosedChar + strCode + strEnclosedChar
+  Else
+    While nPos &lt;&gt; 0
+      ' Build string.
+      strTemp = strTemp + strEnclosedChar + Left$(strCode, nPos - 1) + strEnclosedChar + strDelimiter
+      ' Rebuild string.
+      strCode = Trim$(Mid$(strCode, nPos + 1, Len(strCode)))
+      ' Find subsequent position of delimiter.
+      nPos = InStr(strCode, strDelimiter)
+    WEnd
+    ' Enclose last item.
+    strTemp = strTemp + strEnclosedChar + strCode + strEnclosedChar
+  End If
+  ' Return the string.
+  MakeMultiString = strTemp  
+End Function
+Sub ChangeListItemPosition(ByVal hList As List, ByVal strItem As String, ByVal strColumnTitle As String, ByVal strPositionType As String, ByVal nPosition As Integer)
+  Const sPOSITION_TYPE_FIRST As String = "F"
+  Const sPOSITION_TYPE_LAST As String = "L"
+  Const sPOSITION_TYPE_SPECIFIC As String = "S"
+End Sub
+Sub ProcessGeneralSection(ByVal hField As Fields)
+  Const sFROM_CLIENT As String = "TBMCLNT"
+  hField("_HSF_CHK_GN_IN_ELH").Visible = TRUE
+  hField("_HSF_CHK_GN_EX_ELH").Visible = TRUE
+  hField("_HSF_CHK_GN_SEP_CH").Visible = TRUE
+  hField("_HSF_CHK_GN_SHT_DT").Visible = TRUE
+  hField("_HSF_CHK_GN_CST_TX").Visible = TRUE
+  hField("_HSF_CHK_GN_EXH_RT").Visible = TRUE
+  hField("_HSF_CHK_GN_PT_DTL").Visible = TRUE
+  hField("_HSF_CHK_GN_PT_SUM").Visible = TRUE
+  hField("_HSF_CHK_GN_CL_LCK").Visible = TRUE
+  hField("_HSF_CHK_GN_DT_RNG").Visible = TRUE
+  hField("_HSF_RB_GN_DT_OPT").Visible = TRUE
+  hField("_HSF_GN_LANG_CODE").Visible = TRUE
+  hField("_HSF_GN_LANG_DESC").Visible = TRUE
+  hField("_HSF_GN_PCT_DISC").Visible = TRUE
+  hField("_HSF_CHK_GN_INC_MC").Visible = TRUE
+  hField("_HSF_RB_GN_MC_OP").Visible = TRUE
+  hField("_HSF_CHK_GN_BOC").Visible = TRUE
+  hField("_HSF_EXC_GBL_FEES").Visible = TRUE
+  ' Determine if date range is ticked.
+  If hField("_HSF_CHK_GN_DT_RNG").Value = hField("_HSF_CHK_GN_DT_RNG").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_RB_GN_DT_OPT").Enabled = TRUE
+  Else
+    ' Value is not ticked.
+    hField("_HSF_RB_GN_DT_OPT").Enabled = FALSE
+  End If
+  ' Groupbox.
+  hField("_HSF_BX_GN_ELH").Visible = TRUE
+  hField("_HSF_BX_GN_PT").Visible = TRUE
+  hField("_HSF_BX_GN_DT_RNG").Visible = TRUE
+  hField("_HSF_BX_GN_GS").Visible = TRUE
+  hField("_HSF_BX_GN_CLS").Visible = TRUE
+  hField("_HSF_BX_GN_LNS").Visible = TRUE
+  hField("_HSF_BX_GN_CP_MA").Visible = TRUE
+  hField("_HSF_BX_GN_MC").Visible = TRUE
+  ' Apply To All Matters Button.
+  hField("_HSF_BTTN_GN_AP_MA").Visible = TRUE
+  ' Copy Option Settings.
+  hField("_HSF_GN_CP_MA").Visible = TRUE
+  hField("_HSF_BTTN_GN_CP_MA").Visible = TRUE
+  ' Determine if include matter cost to date is ticked.
+  If hField("_HSF_CHK_GN_INC_MC").Value = hField("_HSF_CHK_GN_INC_MC").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_RB_GN_MC_OP").Enabled = TRUE
+  Else
+    ' Value is not ticked.
+    hField("_HSF_RB_GN_MC_OP").Enabled = FALSE
+  End If
+  ' Determine where the screen is launched from.
+  If gstrCmdExe = sFROM_CLIENT Then
+    ' Launched via client, thus display the Client Settings details.
+    hField("_HSF_BX_GN_CLS").Visible = TRUE
+    hField("_HSF_BTTN_GN_AP_MA").Visible = TRUE
+    hField("_HSF_CHK_GN_CST_TX").Visible = TRUE
+    hField("_HSF_CHK_GN_CL_LCK").Visible = TRUE
+    ' Disable Copy Option items.
+    hField("_HSF_GN_CP_MA").Enabled = FALSE
+    hField("_HSF_BTTN_GN_CP_MA").Enabled = FALSE
+  Else
+    ' Not launched via client, thus hide the Client Settings details.
+    hField("_HSF_BX_GN_CLS").Visible = FALSE
+    hField("_HSF_BTTN_GN_AP_MA").Visible = FALSE
+    hField("_HSF_CHK_GN_CST_TX").Visible = FALSE
+    hField("_HSF_CHK_GN_CL_LCK").Visible = FALSE
+    ' Enable Copy Option items.
+    hField("_HSF_GN_CP_MA").Enabled = TRUE
+    hField("_HSF_BTTN_GN_CP_MA").Enabled = TRUE
+  End If
+End Sub
+Sub ProcessCoverLetterSection(ByVal hField As Fields)
+  Const sCONFIDENTIALITY_OTHER As String = "CO"
+  Const sDUAL_SIGNATURE_OTHER As String = "OT"
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_CL_INCLDE").Value = hField("_HSF_CHK_CL_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_CHK_CL_FIN_DT").Visible = TRUE
+    hField("_HSF_CHK_CL_CNF_IN").Visible = TRUE
+    hField("_HSF_RB_CL_CNF_TYP").Visible = TRUE
+    hField("_HSF_CL_CNF_OTH").Visible = TRUE
+    hField("_HSF_CHK_CL_DS").Visible = TRUE
+    hField("_HSF_RB_CL_DS_TYPE").Visible = TRUE
+    hField("_HSF_CL_DS_OT_EM_C").Visible = TRUE
+    hField("_HSF_CL_DS_OT_EM_N").Visible = TRUE
+    ' Groupbox.
+    hField("_HSF_BX_CL_GS").Visible = TRUE
+    hField("_HSF_BX_CL_CF").Visible = TRUE
+    hField("_HSF_BX_CL_DS").Visible = TRUE
+    hField("_HSF_BX_CL_DS_OTH").Visible = TRUE
+    ' Determine if include confidentiality is ticked.
+    If hField("_HSF_CHK_CL_CNF_IN").Value = hField("_HSF_CHK_CL_CNF_IN").Checkbox.OnValue Then
+      ' Value is ticked.
+      hField("_HSF_RB_CL_CNF_TYP").Enabled = TRUE
+      ' Determine if confidentiality other type is selected.
+      If hField("_HSF_RB_CL_CNF_TYP").Value = sCONFIDENTIALITY_OTHER Then
+        ' Other selected.
+        hField("_HSF_CL_CNF_OTH").Enabled = TRUE
+      Else
+        ' Other not selected.
+        hField("_HSF_CL_CNF_OTH").Enabled = FALSE
+      End If
+    Else
+      ' Value is not ticked.
+      hField("_HSF_RB_CL_CNF_TYP").Enabled = FALSE
+      hField("_HSF_CL_CNF_OTH").Enabled = FALSE
+    End If
+	' Determine if dual signature is ticked.
+    If hField("_HSF_CHK_CL_DS").Value = hField("_HSF_CHK_CL_DS").Checkbox.OnValue Then
+      ' Value is ticked.
+      hField("_HSF_RB_CL_DS_TYPE").Enabled = TRUE
+      hField("_HSF_CL_DS_OT_EM_C").Enabled = TRUE
+      hField("_HSF_CL_DS_OT_EM_N").Enabled = TRUE
+    Else
+      ' Value is not ticked.
+      hField("_HSF_RB_CL_DS_TYPE").Enabled = FALSE
+      hField("_HSF_CL_DS_OT_EM_C").Enabled = FALSE
+      hField("_HSF_CL_DS_OT_EM_N").Enabled = FALSE
+    End If
+    ' Determine if dual signature other type is selected.
+    If hField("_HSF_RB_CL_DS_TYPE").Value = sDUAL_SIGNATURE_OTHER Then
+      ' Other selected.
+      hField("_HSF_CL_DS_OT_EM_C").Enabled = TRUE
+      hField("_HSF_CL_DS_OT_EM_N").Enabled = TRUE
+    Else
+      ' Other not selected.
+      hField("_HSF_CL_DS_OT_EM_C").Enabled = FALSE
+      hField("_HSF_CL_DS_OT_EM_N").Enabled = FALSE
+    End If
+  Else
+    ' Value is not ticked.
+    hField("_HSF_CHK_CL_FIN_DT").Visible = FALSE
+    hField("_HSF_CHK_CL_CNF_IN").Visible = FALSE
+    hField("_HSF_RB_CL_CNF_TYP").Visible = FALSE
+    hField("_HSF_CL_CNF_OTH").Visible = FALSE
+    hField("_HSF_CHK_CL_DS").Visible = FALSE
+    hField("_HSF_RB_CL_DS_TYPE").Visible = FALSE
+    hField("_HSF_CL_DS_OT_EM_C").Visible = FALSE
+    hField("_HSF_CL_DS_OT_EM_N").Visible = FALSE
+    hField("_HSF_BX_CL_GS").Visible = FALSE
+    hField("_HSF_BX_CL_CF").Visible = FALSE
+    hField("_HSF_BX_CL_DS").Visible = FALSE
+    hField("_HSF_BX_CL_DS_OTH").Visible = FALSE
+  End If
+End Sub
+Sub ProcessTimeSummarySection(ByVal hField As Fields)
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_TS_INCLDE").Value = hField("_HSF_CHK_TS_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_CHK_TS_SRT_RK").Visible = TRUE
+    hField("_HSF_CHK_TS_SRT_OD").Visible = TRUE
+    hField("_HSF_TS_LIST_ITEM").Visible = TRUE
+    hField("_HSF_CHK_TS_AVG_RT").Visible = TRUE
+    hField("_HSF_CHK_TS_PA").Visible = TRUE
+    hField("_HSF_CHK_TS_ANL_PA").Visible = TRUE
+    hField("_HSF_LST_TS_AVAIL").Visible = TRUE
+    hField("_HSF_LST_TS_INCL").Visible = TRUE
+    ' Display add and remove section buttons.
+    hField("_HSF_BTTN_TS_ADD").Visible = TRUE
+    hField("_HSF_BTTN_TS_DEL").Visible = TRUE
+    ' Display Available and Included text.
+    hField("_HSF_TXT_AVAIL").Visible = TRUE
+    hField("_HSF_TXT_INCL").Visible = TRUE
+    ' Groupbox.
+    hField("_HSF_BX_GRPING_ORD").Visible = TRUE
+    hField("_HSF_BX_PL").Visible = TRUE
+    ' Determine if summarise paralegal options are ticked.
+    If ( hField("_HSF_CHK_TS_PA").Value = hField("_HSF_CHK_TS_PA").Checkbox.OnValue Or hField("_HSF_CHK_TS_ANL_PA").Value = hField("_HSF_CHK_TS_ANL_PA").Checkbox.OnValue) Then
+      ' Value is ticked.
+      hField("_HSF_CHK_TS_AVG_RT").Enabled = TRUE
+    Else
+      ' Value is not ticked.
+      hField("_HSF_CHK_TS_AVG_RT").Enabled = FALSE
+    End If
+  Else
+    ' Value is not ticked.
+    hField("_HSF_CHK_TS_SRT_RK").Visible = FALSE
+    hField("_HSF_CHK_TS_SRT_OD").Visible = FALSE
+    hField("_HSF_TS_LIST_ITEM").Visible = FALSE
+    hField("_HSF_CHK_TS_AVG_RT").Visible = FALSE
+    hField("_HSF_CHK_TS_PA").Visible = FALSE
+    hField("_HSF_CHK_TS_ANL_PA").Visible = FALSE
+    hField("_HSF_LST_TS_AVAIL").Visible = FALSE
+    hField("_HSF_LST_TS_INCL").Visible = FALSE
+    hField("_HSF_BTTN_TS_ADD").Visible = FALSE
+    hField("_HSF_BTTN_TS_DEL").Visible = FALSE
+    hField("_HSF_TXT_AVAIL").Visible = FALSE
+    hField("_HSF_TXT_INCL").Visible = FALSE
+    hField("_HSF_BX_GRPING_ORD").Visible = FALSE
+    hField("_HSF_BX_PL").Visible = FALSE
+  End If
+End Sub
+Sub ProcessTimeDetailSection(ByVal hField As Fields)
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_TD_INCLDE").Value = hField("_HSF_CHK_TD_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_TD_LIST_ITEM").Visible = TRUE
+    hField("_HSF_LST_TD_AVAIL").Visible = TRUE
+    hField("_HSF_LST_TD_INCL").Visible = TRUE
+    ' Display add and remove section buttons.
+    hField("_HSF_BTTN_TD_ADD").Visible = TRUE
+    hField("_HSF_BTTN_TD_DEL").Visible = TRUE
+    ' Display Available and Included text.
+    hField("_HSF_TXT_AVAIL").Visible = TRUE
+    hField("_HSF_TXT_INCL").Visible = TRUE
+  Else
+    ' Value is not ticked.
+    hField("_HSF_TD_LIST_ITEM").Visible = FALSE
+    hField("_HSF_LST_TD_AVAIL").Visible = FALSE
+    hField("_HSF_LST_TD_INCL").Visible = FALSE
+    hField("_HSF_BTTN_TD_ADD").Visible = FALSE
+    hField("_HSF_BTTN_TD_DEL").Visible = FALSE
+    hField("_HSF_TXT_AVAIL").Visible = FALSE
+    hField("_HSF_TXT_INCL").Visible = FALSE
+  End If 
+End Sub
+Sub ProcessDisbSummarySection(ByVal hField As Fields)
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_DS_INCLDE").Value = hField("_HSF_CHK_DS_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_CHK_DS_SRT_DB").Visible = TRUE
+    hField("_HSF_DS_LIST_ITEM").Visible = TRUE
+    hField("_HSF_LST_DS_AVAIL").Visible = TRUE
+    hField("_HSF_LST_DS_INCL").Visible = TRUE
+    ' Display add and remove section buttons.
+    hField("_HSF_BTTN_DS_ADD").Visible = TRUE
+    hField("_HSF_BTTN_DS_DEL").Visible = TRUE
+    ' Display Available and Included text.
+    hField("_HSF_TXT_AVAIL").Visible = TRUE
+    hField("_HSF_TXT_INCL").Visible = TRUE
+    ' Display Grouping Order.
+    hField("_HSF_BX_GRPING_ORD").Visible = TRUE
+  Else
+    ' Value is not ticked.
+    hField("_HSF_CHK_DS_SRT_DB").Visible = FALSE
+    hField("_HSF_DS_LIST_ITEM").Visible = FALSE
+    hField("_HSF_LST_DS_AVAIL").Visible = FALSE
+    hField("_HSF_LST_DS_INCL").Visible = FALSE
+    hField("_HSF_BTTN_DS_ADD").Visible = FALSE
+    hField("_HSF_BTTN_DS_DEL").Visible = FALSE
+    hField("_HSF_TXT_AVAIL").Visible = FALSE
+    hField("_HSF_TXT_INCL").Visible = FALSE
+    hField("_HSF_BX_GRPING_ORD").Visible = FALSE
+  End If
+End Sub
+Sub ProcessDisbDetailSection(ByVal hField As Fields)
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_DD_INCLDE").Value = hField("_HSF_CHK_DD_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_CHK_DD_DI_ALL").Visible = TRUE
+    hField("_HSF_DD_ITEM_LIST").Visible = TRUE
+    hField("_HSF_DD_LIST_DISB").Visible = TRUE
+    hField("_HSF_LST_DD_AVAIL").Visible = TRUE
+    hField("_HSF_LST_DD_INCL").Visible = TRUE
+    hField("_HSF_LST_DD_DI_AVL").Visible = TRUE
+    hField("_HSF_LST_DD_DI_INC").Visible = TRUE
+    ' Display add and remove section buttons.
+    hField("_HSF_BTTN_DD_ADD").Visible = TRUE
+    hField("_HSF_BTTN_DD_DEL").Visible = TRUE
+    hField("_HSF_BTTN_DD_DI_AD").Visible = TRUE
+    hField("_HSF_BTTN_DD_DI_DL").Visible = TRUE
+    ' Determine if display all disbursement is ticked.
+    If hField("_HSF_CHK_DD_DI_ALL").Value = hField("_HSF_CHK_DD_DI_ALL").Checkbox.OnValue Then
+      ' Value is ticked.
+      hField("_HSF_LST_DD_DI_AVL").Visible = FALSE
+      hField("_HSF_LST_DD_DI_INC").Visible = FALSE
+      hField("_HSF_TXT_DI_AVL").Visible = FALSE
+      hField("_HSF_TXT_DI_INC").Visible = FALSE
+      hField("_HSF_BTTN_DD_DI_AD").Visible = FALSE
+      hField("_HSF_BTTN_DD_DI_DL").Visible = FALSE
+    Else
+      ' Value is not ticked.
+      hField("_HSF_LST_DD_DI_AVL").Visible = TRUE
+      hField("_HSF_LST_DD_DI_INC").Visible = TRUE
+      hField("_HSF_TXT_DI_AVL").Visible = TRUE
+      hField("_HSF_TXT_DI_INC").Visible = TRUE
+      hField("_HSF_BTTN_DD_DI_AD").Visible = TRUE
+      hField("_HSF_BTTN_DD_DI_DL").Visible = TRUE
+    End If
+    ' Display Available and Included text.
+    hField("_HSF_TXT_AVAIL").Visible = TRUE
+    hField("_HSF_TXT_INCL").Visible = TRUE
+  Else
+    hField("_HSF_CHK_DD_DI_ALL").Visible = FALSE
+    hField("_HSF_DD_ITEM_LIST").Visible = FALSE
+    hField("_HSF_DD_LIST_DISB").Visible = FALSE
+    hField("_HSF_LST_DD_AVAIL").Visible = FALSE
+    hField("_HSF_LST_DD_INCL").Visible = FALSE
+    hField("_HSF_LST_DD_DI_AVL").Visible = FALSE
+    hField("_HSF_LST_DD_DI_INC").Visible = FALSE
+    hField("_HSF_LST_DD_DI_AVL").Visible = FALSE
+    hField("_HSF_LST_DD_DI_INC").Visible = FALSE
+    hField("_HSF_TXT_DI_AVL").Visible = FALSE
+    hField("_HSF_TXT_DI_INC").Visible = FALSE
+    hField("_HSF_BTTN_DD_ADD").Visible = FALSE
+    hField("_HSF_BTTN_DD_DEL").Visible = FALSE
+    hField("_HSF_BTTN_DD_DI_AD").Visible = FALSE
+    hField("_HSF_BTTN_DD_DI_DL").Visible = FALSE
+    hField("_HSF_TXT_AVAIL").Visible = FALSE
+    hField("_HSF_TXT_INCL").Visible = FALSE
+  End If
+End Sub
+Sub AllocateDeallocateIncludeList(ByVal hSourceList As List, ByVal hDestinationList As List, ByVal strArea As String)
+  Const sSECTION_TIME_SUMMARY As String = "TS"
+  Const sSECTION_TIME_DETAIL As String = "TD"
+  Const sSECTION_DISB_SUMMARY As String = "DS"
+  Const sSECTION_DISB_DETAIL As String = "DD"
+  Const sSECTION_DISB_DETAIL_DISB_ONLY As String = "DDDI"
+  Const sCOLUMN_TITLE_ROW_UNO As String = "Row Uno"
+  Const sCOLUMN_TITLE_DD_NAME As String = "DD Name"
+  Const sCOLUMN_TITLE_TIME_FIELD As String = "Time Field"
+  Const sCOLUMN_TITLE_DISB_FIELD As String = "Disbursement Field"
+  Const sCOLUMN_TITLE_DISB_CODE As String = "Disbursement Type"
+  Const sCOLUMN_TITLE_DESCRIPTION As String = "Description"
+  Const sCOLUMN_TITLE_MIN_SIZE As String = "Min Size"
+  Const sCOLUMN_TITLE_MAX_SIZE As String = "Max Size"
+  Dim nRows As Long
+  Dim nLoop As Long
+  Dim strRowUno As String
+  Dim strDDName As String
+  Dim strField As String
+  Dim strDesc As String
+  DIm strMinSize As String
+  Dim strMaxSize As String
+  Dim strData As String
+  ' Obtain number of rows in source list. 
+  nRows = hSourceList.Count
+  ' Loop through source list .
+  For nLoop = 1 To nRows
+    ' Determine if current source row is selected.
+    If hSourceList.Selected(nLoop) Then
+      ' Determine if using disbursement detail disbursement code list.
+      If strArea &lt;&gt; sSECTION_DISB_DETAIL_DISB_ONLY Then
+        ' Not disbursement code list.
+        ' Obtain information from selected row.
+        strRowUno = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_ROW_UNO))
+        strDDName = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_DD_NAME))
+        ' Determine the section area.
+        Select Case strArea
+          Case sSECTION_TIME_SUMMARY, sSECTION_TIME_DETAIL
+            strField = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_TIME_FIELD))
+          Case sSECTION_DISB_SUMMARY, sSECTION_DISB_DETAIL
+            strField = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_DISB_FIELD))
+        End Select
+        strDesc = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_DESCRIPTION))
+        strMinSize = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_MIN_SIZE))
+        strMaxSize = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_MAX_SIZE))
+        ' Build row data.
+        strData = strRowUno + ebTAB
+        strData = strData + strDDName + ebTAB
+        strData = strData + strField + ebTAB
+        strData = strData + strDesc + ebTAB
+        strData = strData + strMinSize + ebTAB
+        strData = strData + strMaxSize
+      Else
+        ' Disbursement code list.
+        strDDName = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_DISB_CODE))
+        strDesc = hSourceList.RowItem(nLoop, hSourceList.FindColumn(sCOLUMN_TITLE_DESCRIPTION))
+        ' Build row data.
+        strData = strDDName + ebTAB
+        strData = strData + strDesc
+      End If
+      ' Add row to destination list.
+      hDestinationList.AddRow strData
+    End If
+  Next nLoop
+  ' Loop through source list backwards to take care of the deletion.
+  For nLoop = nRows To 1 Step -1 
+    ' Determine if current source row is selected.
+    If hSourceList.Selected(nLoop) Then
+      ' Remove the row in the source list.
+      hSourceList.DeleteRow nLoop
+    End If
+  Next nLoop
+End Sub
+Sub LoadAvailable(ByVal hList As List, ByVal strArea As String, ByVal strCode As String)
+  Const sDELIMITER_COMMA As String = ","
+  Const sSINGLE_QUOTE As String = "'"
+  Const sSECTION_DISB_DETAIL_DISB_ONLY As String = "DDDI"
+  Dim hSQL As New SQLAccess
+  Dim strSQL As String
+  Dim strData As String
+  ' Determine if items already selected.
+  If Trim$(strCode) &lt;&gt; "" Then
+    ' Enclose string codes in single quotes.
+    strCode = MakeMultiString(strCode, sDELIMITER_COMMA, sSINGLE_QUOTE)
+  End If
+  ' AVALABLE LIST
+  ' Clear the listbox content.
+  hList.ClearList
+  ' Determine if disbursement code list.
+  If strArea &lt;&gt; sSECTION_DISB_DETAIL_DISB_ONLY Then
+    ' Not disbursement code list.
+    ' Obtain available items.
+    strSQL = "SELECT ROW_UNO,"
+    strSQL = strSQL + " DD_NAME,"
+    strSQL = strSQL + " DISP_CODE,"
+    strSQL = strSQL + " DISP_DESC,"
+    strSQL = strSQL + " MIN_SIZE,"
+    strSQL = strSQL + " MAX_SIZE"
+    strSQL = strSQL + " FROM _HSF_HBL_INVOICE_OPTION"
+    strSQL = strSQL + " WHERE INACTIVE = 'N'"
+    ' Determine if area is provided.
+    If Trim$(strArea) &lt;&gt; "" Then
+      ' Filter by area
+      strSQL = strSQL + " AND AREA = '" + UCase$(strArea) + "'"
+    End If
+    ' Determine if items already selected.
+    If Trim$(strCode) &lt;&gt; "" Then
+      ' Available filter.
+      strSQL = strSQL + " AND DD_NAME NOT IN (" + strCode + ")"
+    End If
+    strSQL = strSQL + " ORDER BY DISP_CODE"
+  Else
+    ' Disbursement code list.
+    ' Obtain available items.
+    strSQL = "SELECT COST_CODE,"
+    strSQL = strSQL + " COST_DESC,"
+    strSQL = strSQL + " DISBGRP_CODE"
+    strSQL = strSQL + " FROM CDL_COST"
+    strSQL = strSQL + " WHERE INACTIVE = 'N'"
+    ' Determine if items already selected.
+    If Trim$(strCode) &lt;&gt; "" Then
+      ' Available filter.
+      strSQL = strSQL + " AND COST_CODE NOT IN (" + strCode + ")"
+    End If
+    strSQL = strSQL + " ORDER BY COST_DESC"
+  End If
+  ' Execute SQL.
+  hSQL.IssueCommand strSQL
+  ' Determine if any errors or no results.
+  If (hSQL.Status = SQLERR_NONE And hSQL.Status &lt;&gt; SQLERR_NOROWS) Then
+    ' No SQL errors and there are results returned.
+    ' Loop through result set. 	  
+    While Not(hSQL.AllRowsRead)
+      ' Determine if disbursement code list.
+      If strArea &lt;&gt; sSECTION_DISB_DETAIL_DISB_ONLY Then
+        ' Not disbursement code list.
+        ' Build the display data.
+        strData = Trim$(hSQL.Value("ROW_UNO")) + ebTAB
+        strData = strData + Trim$(hSQL.Value("DD_NAME")) + ebTAB
+        strData = strData + Trim$(hSQL.Value("DISP_CODE")) + ebTAB
+        strData = strData + Trim$(hSQL.Value("DISP_DESC")) + ebTAB
+        strData = strData + Trim$(hSQL.Value("MIN_SIZE")) + ebTAB
+        strData = strData + Trim$(hSQL.Value("MAX_SIZE"))
+      Else
+        ' Disbursement code list.
+        strData = Trim$(hSQL.Value("COST_CODE")) + ebTAB
+        strData = strData + Trim$(hSQL.Value("COST_DESC"))
+      End If
+      ' Add row to list box. 
+      hList.AddRow strData
+      ' Increment row counter.
+      hSQL.Row = hSQL.Row + 1
+    WEnd
+  End If ' No SQL Errors And Rows Returned.
+  ' Release object handle.
+  Set hSQL = Nothing
+End Sub
+Sub LoadSelected(ByVal hList As List, ByVal strArea As String, ByVal strCode As String)
+  Const sDELIMITER_COMMA As String = ","
+  Const sSINGLE_QUOTE As String = "'"
+  Const sSECTION_DISB_DETAIL_DISB_ONLY As String = "DDDI"
+  Dim hSQL As New SQLAccess
+  Dim strSQL As String
+  Dim strData As String
+  Dim strItem As String
+  Dim nLoop As Long
+  ' Determine if items already selected.
+  If Trim$(strCode) &lt;&gt; "" Then
+    ' Enclose string codes in single quotes.
+    strCode = MakeMultiString(strCode, sDELIMITER_COMMA, sSINGLE_QUOTE)
+  End If
+  ' Clear the listbox content.
+  hList.ClearList
+  ' Determine if any items already selected.
+  If Trim$(strCode) &lt;&gt; "" Then
+    ' Determine if disbursement code list.
+    If strArea &lt;&gt; sSECTION_DISB_DETAIL_DISB_ONLY Then
+      ' Not disbursement code list.
+      ' Initialise variables.
+      nLoop = 1
+      ' Obtain first item from list.     
+      strItem = Trim$(Item$(strCode, nLoop))
+      ' Loop through list items.     
+      While strItem &lt;&gt; ""
+        ' Obtain available items.
+        strSQL = "SELECT ROW_UNO,"
+        strSQL = strSQL + " DD_NAME,"
+        strSQL = strSQL + " DISP_CODE,"
+        strSQL = strSQL + " DISP_DESC,"
+        strSQL = strSQL + " MIN_SIZE,"
+        strSQL = strSQL + " MAX_SIZE"
+        strSQL = strSQL + " FROM _HSF_HBL_INVOICE_OPTION"
+        strSQL = strSQL + " WHERE INACTIVE = 'N'"
+        ' Determine if area is provided.
+        If Trim$(strArea) &lt;&gt; "" Then
+          ' Filter by area
+          strSQL = strSQL + " AND AREA = '" + UCase$(strArea) + "'"
+        End If
+        ' Determine if items already selected.
+        If Trim$(strCode) &lt;&gt; "" Then
+          ' Selected filter.
+          strSQL = strSQL + " AND DD_NAME IN (" + strItem + ")"
+        End If
+        ' Execute SQL.
+        hSQL.IssueCommand strSQL
+        ' Determine if any errors or no results.
+        If (hSQL.Status = SQLERR_NONE And hSQL.Status &lt;&gt; SQLERR_NOROWS) Then
+          ' No SQL errors and there are results returned.
+          ' Not disbursement code list.
+          ' Build the display data.
+          strData = Trim$(hSQL.Value("ROW_UNO")) + ebTAB
+          strData = strData + Trim$(hSQL.Value("DD_NAME")) + ebTAB
+          strData = strData + Trim$(hSQL.Value("DISP_CODE")) + ebTAB
+          strData = strData + Trim$(hSQL.Value("DISP_DESC")) + ebTAB
+          strData = strData + Trim$(hSQL.Value("MIN_SIZE")) + ebTAB
+          strData = strData + Trim$(hSQL.Value("MAX_SIZE"))
+          ' Add row to list box. 
+          hList.AddRow strData
+        End If ' No SQL Errors And Rows Returned.
+        nLoop = nLoop + 1
+        strItem = Trim$(Item$(strCode, nLoop))
+      WEnd
+    Else
+      ' Disbursement code list.
+      ' Obtain selected items.
+      strSQL = "SELECT COST_CODE,"
+      strSQL = strSQL + " COST_DESC,"
+      strSQL = strSQL + " DISBGRP_CODE"
+      strSQL = strSQL + " FROM CDL_COST"
+      strSQL = strSQL + " WHERE INACTIVE = 'N'"
+      ' Determine if items already selected.
+      If Trim$(strCode) &lt;&gt; "" Then
+        ' Selected filter.
+        strSQL = strSQL + " AND COST_CODE IN (" + strCode + ")"
+      End If
+      strSQL = strSQL + " ORDER BY COST_CODE"
+      ' Execute SQL.
+      hSQL.IssueCommand strSQL
+      ' Determine if any errors or no results.
+      If (hSQL.Status = SQLERR_NONE And hSQL.Status &lt;&gt; SQLERR_NOROWS) Then
+        ' No SQL errors and there are results returned.
+        ' Loop through result set. 	  
+        While Not(hSQL.AllRowsRead)
+          ' Disbursement code list.
+          strData = Trim$(hSQL.Value("COST_CODE")) + ebTAB
+          strData = strData + Trim$(hSQL.Value("COST_DESC"))
+          ' Add row to list box. 
+          hList.AddRow strData
+          ' Increment row counter.
+          hSQL.Row = hSQL.Row + 1
+        WEnd
+      End If ' No SQL Errors And Rows Returned.
+    End If
+  End If ' Selected Items Check.
+  ' Release object handle.
+  Set hSQL = Nothing
+End Sub
+Sub HideAll(ByVal hField As Fields)
+  Dim nLoop As Long
+  ' Loop through all objects.
+  For nLoop = 1 To hField.Count
+    ' Determine if current object is a button.
+    If hField(nLoop).ObjectType &lt;&gt; O_BUTTON then
+      ' Current object not button, thus hide it.
+      hField(nLoop).Visible = FALSE
+    End If
+  Next nLoop
+  ' Unhide the group boxes.
+  hField("_HSF_BX_HEADER").Visible = TRUE
+  ' Unhide the header information.
+  hField("_HSF_CLIENT_CODE").Visible = TRUE
+  hField("_HSF_CLIENT_NAME").Visible = TRUE
+  hField("_HSF_MATTER_CODE").Visible = TRUE
+  hField("_HSF_MATTER_NAME").Visible = TRUE
+End Sub
+Sub SectionArea(ByVal hField As Fields, ByVal strSection As String)
+  Const sSECTION_GENERAL As String = "GN"
+  Const sSECTION_COVER_LETTER As String = "CL"
+  Const sSECTION_TIME_SUMMARY As String = "TS"
+  Const sSECTION_TIME_DETAIL As String = "TD"
+  Const sSECTION_DISB_SUMMARY As String = "DS"
+  Const sSECTION_DISB_DETAIL As String = "DD"
+  Const sCONFIDENTIALITY_OTHER As String = "CO"
+  Const sDUAL_SIGNATURE_OTHER As String = "OT"
+  ' Hide all fields.
+  Call HideAll(hField)
+  ' Hide Add and Remove section buttons.
+  hField("_HSF_BTTN_TS_ADD").Visible = FALSE
+  hField("_HSF_BTTN_TS_DEL").Visible = FALSE
+  hField("_HSF_BTTN_TD_ADD").Visible = FALSE
+  hField("_HSF_BTTN_TD_DEL").Visible = FALSE
+  hField("_HSF_BTTN_DS_ADD").Visible = FALSE
+  hField("_HSF_BTTN_DS_DEL").Visible = FALSE
+  hField("_HSF_BTTN_DD_ADD").Visible = FALSE
+  hField("_HSF_BTTN_DD_DEL").Visible = FALSE
+  hField("_HSF_BTTN_DD_DI_AD").Visible = FALSE
+  hField("_HSF_BTTN_DD_DI_DL").Visible = FALSE
+  hField("_HSF_BTTN_GN_AP_MA").Visible = FALSE
+  hField("_HSF_BTTN_GN_CP_MA").Visible = FALSE
+  ' Version number text.
+  hField("_TXT_VERSION").Visible = TRUE
+  Select Case strSection
+    Case sSECTION_GENERAL
+      ' General Section
+      Call ProcessGeneralSection(hField)
+    Case sSECTION_COVER_LETTER
+      ' Cover Letter Section
+      hField("_HSF_CHK_CL_INCLDE").Visible = TRUE
+      Call ProcessCoverLetterSection(hField)     
+    Case sSECTION_TIME_SUMMARY
+      ' Time Summary Section
+      hField("_HSF_CHK_TS_INCLDE").Visible = TRUE
+      Call ProcessTimeSummarySection(hField)     
+    Case sSECTION_TIME_DETAIL
+      ' Time Detail Section
+      hField("_HSF_CHK_TD_INCLDE").Visible = TRUE
+      Call ProcessTimeDetailSection(hField)     
+    Case sSECTION_DISB_SUMMARY
+      ' Disb Summary Section
+      hField("_HSF_CHK_DS_INCLDE").Visible = TRUE
+      Call ProcessDisbSummarySection(hField)     
+    Case sSECTION_DISB_DETAIL
+      ' Disb Detail Section
+      hField("_HSF_CHK_DD_INCLDE").Visible = TRUE
+      Call ProcessDisbDetailSection(hField)     
+    Case Else
+      ' General Section
+      Call ProcessGeneralSection(hField)
+  End Select
+End Sub
+Sub AfterInsert()
+  Const sFROM_CLIENT As String = "TBMCLNT"
+  Const sFROM_MATTER As String = "TBMMATT3"
+  Dim hField As Fields
+  Dim hSQL As New SQLAccess
+  Dim strSQL As String
+  Dim strOptUno As String
+  Dim strMatterCode As String
+  Dim strMsg As String
+  Dim nResponse As String
+  ' Obtain object handle.
+  Set hField = ThisField.Form.Fields
+  ' Obtain the new option key.
+  strOptUno = Trim$(hField("OPT_UNO").Value)
+  ' Obtain matter code
+  strMatterCode = Trim$(hField("_HSF_MATTER_CODE").Value)
+  ' Determine where the screen is launched from and set the header information.
+  If (gstrCmdExe &lt;&gt; sFROM_CLIENT And gstrCmdExe &lt;&gt; sFROM_MATTER) Then
+    ' Calling from the billing desktop.
+    ' Determine if a matter billing key is provided.
+    If gstrBillMUno &lt;&gt; "" Then
+      ' Matter billing key provided, thus update it with the new option key.
+      strSQL = "UPDATE BLT_BILLM"
+      strSQL = strSQL + " SET OPT_UNO = " + strOptUno + ","
+      strSQL = strSQL + " LAST_MODIFIED = GETDATE()"
+      strSQL = strSQL + " WHERE BILLM_UNO = " + gstrBillMUno
+      ' Execute SQL statement.
+      hSQL.IssueCommand strSQL
+    End If  ' Matter Billing Provided Check
+    ' Obtain confirmation from user if new option key should be applied back to the matter.
+    ' Build and display confirmation.
+    strMsg = "Would you like to save these settings permanently? If you select No these settings will be used for only this bill."
+    nResponse = YesNoMessage(strMsg)
+    ' Determine user response.
+    If nResponse = BUTTON_YES Then
+      ' Determine if matter is provided.
+      If strMatterCode &lt;&gt; "" Then
+        ' User confirms that new option key should be applied back to the matter.
+        strSQL = "UPDATE TM"
+        strSQL = strSQL + " SET OPT_UNO = " + strOptUno + ","
+        strSQL = strSQL + " LAST_MODIFIED = GETDATE()"
+        strSQL = strSQL + " FROM HBM_MATTER M INNER JOIN TBM_MATTER TM"
+        strSQL = strSQL + " ON M.MATTER_UNO = TM.MATTER_UNO"
+        strSQL = strSQL + " WHERE M.MATTER_CODE = '" + strMatterCode + "'"
+        ' Execute SQL statement.
+        hSQL.IssueCommand strSQL
+      End If  ' Matter Provided Check
+    End If  ' User Response Check
+  End If  ' Launch From Billing Desktop Check
+  ' Release object handle.
+  Set hField = Nothing
+  Set hSQL = Nothing
+End Sub
+Function ValidateRecord() As Integer
+  Const sOPTION_VALIDATION_ERROR_SCREEN As String = "_HSF_OPTION_VAL_ERR"
+  Const nMAX_ARRAY_SLOT As Long = 40
+  Const nMAX_ITEMS As Long = 6
+  Const sSECTION_TIME_SUMMARY As String = "Time Summary"
+  Const sSECTION_TIME_DETAIL As String = "Time Detail"
+  Const sSECTION_DISB_SUMMARY As String = "Disb Summary"
+  Const sSECTION_DISB_DETAIL As String = "Disb Detail"
+  Const sCOLUMN_TITLE_TO_SEARCH As String  = "DD Name"
+  Const sLIST_ITEM_TIME_TKPR_CODE As String  = "t_tkpr"
+  Const sLIST_ITEM_TIME_TKPR_INIT As String  = "t_tkpr_init"
+  Const sLIST_ITEM_TIME_TKPR_NAME As String  = "t_tkpr_name"
+  Const sLIST_ITEM_TIME_RANK As String  = "t_rank"
+  Const sLIST_ITEM_TIME_STD_AMT As String  = "t_pcur_samt"
+  Const sLIST_ITEM_TIME_BILL_AMT As String  = "t_pcur_amt"
+  Const sLIST_ITEM_TIME_STD_RATE As String  = "_hsf_t_sratex"
+  Const sLIST_ITEM_TIME_BILL_RATE As String  = "t_rate"
+  Const sLIST_ITEM_TIME_TRAN_DATE As String  = "t_date"
+  Const sLIST_ITEM_BULLET As String  = "d_bullet"
+  Const sLIST_ITEM_TIME_CLNT_PHASE As String  = "t_client_phase"
+  Const sLIST_ITEM_TIME_CLNT_TASK As String  = "t_client_task"
+  Const sLIST_ITEM_TIME_ACTIVITY As String  = "t_activity"
+  Const sLIST_ITEM_TIME_NARRATIVE As String  = "t_narrative"
+  Const sLIST_ITEM_TIME_NARRATIVE_LOC_1 As Integer = 2
+  Const sLIST_ITEM_TIME_NARRATIVE_LOC_2 As Integer = 3
+  Const sLIST_ITEM_DISB_TKPR_CODE As String  = "d_tkpr"
+  Const sLIST_ITEM_DISB_TKPR_NAME As String  = "d_tkpr_name"
+  Const sLIST_ITEM_DISB_CLNT_PHASE As String  = "d_client_phase"
+  Const sLIST_ITEM_DISB_CLNT_TASK As String  = "d_client_task"
+  Const sLIST_ITEM_DISB_COST_CODE As String  = "d_cost"
+  Const sLIST_ITEM_DISB_COST_DESC As String  = "d_cost_desc"
+  Const sLIST_ITEM_DISB_GROUP_CODE As String  = "d_group"
+  Const sLIST_ITEM_DISB_GROUP_DESC As String  = "d_group_desc"
+  Const sLIST_ITEM_DISB_TRAN_DATE As String  = "d_date"
+  Const sLIST_ITEM_DISB_NARRATIVE As String  = "d_narrative"
+  Const sLIST_ITEM_DISB_BILL_AMT As String  = "d_pcur_amt"
+  Const sLIST_ITEM_DISB_NARRATIVE_LOC_1 As Integer = 1
+  Const sLIST_ITEM_DISB_NARRATIVE_LOC_2 As Integer = 2
+  Const sLIST_ITEM_DISB_NARRATIVE_LOC_3 As Integer = 3
+  Dim hDestinationListTS As List
+  Dim hDestinationListTD As List
+  Dim hDestinationListDS As List
+  Dim hDestinationListDD As List
+  Dim hField As Fields
+  Dim strData As String
+  Dim nErrorCount As Long
+  Dim strErrorMsg As String
+  Dim arErrors() As String
+  Dim nArraySlot As Long
+  Dim nLoop As Long
+  Dim hForm As New PopUpForm
+  Dim nItemPosition1 As Integer
+  Dim nItemPosition2 As Integer
+  Dim nItemPosition3 As Integer
+  Dim nItemPosition4 As Integer
+  Set hField = ThisField.Form.Fields
+  Set hDestinationListTS = hField("_HSF_LST_TS_INCL").List
+  Set hDestinationListTD = hField("_HSF_LST_TD_INCL").List
+  Set hDestinationListDS = hField("_HSF_LST_DS_INCL").List
+  Set hDestinationListDD = hField("_HSF_LST_DD_INCL").List
+  ReDim arErrors(nMAX_ARRAY_SLOT)
+  ' Initialise variable.
+  nErrorCount = 0
+  nArraySlot = 0
+  ' List Item Validations:
+  ' TIME SUMMARY
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_TS_INCLDE").Value = hField("_HSF_CHK_TS_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    ' 1) Determine if timekeeper name is selected.
+    nItemPosition1 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_TKPR_NAME, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Timekeeper name is selected.
+      ' Determine if the timekeeper code is selected.
+      nItemPosition2 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_TKPR_CODE, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition2 &gt; 0) Then
+        ' Timekeeper code is selected, check if the code is close to the timekeeper name.
+        If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) And (nItemPosition2 &lt;&gt; (nItemPosition1 - 1) And nItemPosition1 &gt; 1 ) ) Then
+          ' Timekeeper code and name are not next to each other.
+          nErrorCount = nErrorCount + 1
+          strErrorMsg = sSECTION_TIME_SUMMARY + ebTAB + "The Timekeeper Code and Timekeeper Name MUST be selected next to each other."
+          ' Hold error message in a string array.
+          arErrors(nArraySlot) = strErrorMsg
+          ' Increment array slot counter.
+          nArraySlot = nArraySlot + 1
+        End If
+      End If
+    End If
+    ' 2) Determine if standard rate and bill amount are selected.
+    nItemPosition1 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_BILL_AMT, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Billed amount is selected.
+      ' Determine if standard rate is selected.
+      nItemPosition2 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_STD_RATE, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition2 &gt; 0) Then
+        ' Determine if billed rate is selected.
+        nItemPosition3 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_BILL_RATE, sCOLUMN_TITLE_TO_SEARCH)
+        If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0 And nItemPosition3 = 0) Then
+          ' Billed rate not selected.
+          ' Increment error counter.
+          nErrorCount = nErrorCount + 1
+          strErrorMsg = sSECTION_TIME_SUMMARY + ebTAB + "The Billed Amount and Standard Rate was selected but no Billed Rate was selected. Billed Rate MUST also be selected with Billed Amount and Standard Rate."
+          ' Hold error message in a string array.
+          arErrors(nArraySlot) = strErrorMsg
+          ' Increment array slot counter.
+          nArraySlot = nArraySlot + 1
+        End If
+      End If
+      ' Determine if the billed amount is the last selected item.
+      If nItemPosition1 &lt;&gt; hDestinationListTS.Count Then
+        ' Billed amount not last item selected.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_SUMMARY + ebTAB + "The Billed Amount MUST be selected in the LAST position."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    Else
+      ' Billed amount not selected.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_TIME_SUMMARY + ebTAB + "The Billed Amount MUST be selected as it is a MANDATORY item."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+    ' 3) Determine if standard amount is selected.
+    nItemPosition1 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_STD_AMT, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Standard amount is selected
+      ' Determine if billed amount is selected.
+      nItemPosition2 = FindListItem(hDestinationListTS, sLIST_ITEM_TIME_BILL_AMT, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition1 &gt; 0 And nItemPosition2 = 0) Then
+        ' Billed amount not selected.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_SUMMARY + ebTAB + "The Standard Amount was selected but no Billed Amount was selected. Billed Amount MUST also be selected with Standard Amount."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 4) Determine if selected items has exceeded maximum allow.
+    If (hDestinationListTS.Count &gt; nMAX_ITEMS) Then
+      ' Selected items.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_TIME_SUMMARY + ebTAB + "The number of items selected has exceeded the maximum number (" + CStr(nMAX_ITEMS) + ") allowed."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+  End If  ' Time Summary Flag Check.
+  ' TIME DETAIL
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_TD_INCLDE").Value = hField("_HSF_CHK_TD_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    ' 1) Determine if transaction date or bullet is selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TRAN_DATE, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Transaction date is selected, thus check if bullet is also selected.
+      nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_BULLET, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition2 &gt; 0) Then
+        ' Both transaction date and bullet selected.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "Both the Transaction Date and Bullet Point was selected. Only ONE of the items can be selected."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+      ' Determine if transaction date is in first position.
+      If (nItemPosition1 &lt;&gt; 1 And nItemPosition2 = 0) Then
+        ' Transaction date not first position. 
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Transaction Date MUST be selected in the FIRST position."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    Else
+      ' Determine if bullet is selected.
+      nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_BULLET, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition1 &gt; 0) Then
+        ' Bullet is selected, thus check if transaction date is also selected.
+        nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TRAN_DATE, sCOLUMN_TITLE_TO_SEARCH)
+        If (nItemPosition2 &gt; 0) Then
+          ' Both transaction date and bullet selected.
+          ' Increment error counter.
+          nErrorCount = nErrorCount + 1
+          strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "Both the Transaction Date and Bullet Point was selected. Only ONE of the items can be selected."
+          ' Hold error message in a string array.
+          arErrors(nArraySlot) = strErrorMsg
+          ' Increment array slot counter.
+          nArraySlot = nArraySlot + 1
+        End If
+        ' Determine if bullet is in first position.
+        If (nItemPosition1 &lt;&gt; 1 And nItemPosition2 = 0) Then
+          ' Bullet not in first position.
+          ' Increment error counter.
+          nErrorCount = nErrorCount + 1
+          strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Bullet Point MUST be selected in the FIRST position."
+          ' Hold error message in a string array.
+           arErrors(nArraySlot) = strErrorMsg
+          ' Increment array slot counter.
+          nArraySlot = nArraySlot + 1
+        End If
+      End If
+    End If
+    ' 2) Determine if timekeeper name is selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TKPR_NAME, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Timekeeper name is selected.
+      ' Determine if the timekeeper code is selected.
+      nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TKPR_CODE, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition2 &gt; 0) Then
+        ' Timekeeper code is selected, check if the code is close to the timekeeper name.
+        If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) And (nItemPosition2 &lt;&gt; (nItemPosition1 - 1) And nItemPosition1 &gt; 1 ) ) Then
+          ' Timekeeper code and name are not next to each other.
+          nErrorCount = nErrorCount + 1
+          strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Timekeeper Code and Timekeeper Name MUST be selected NEXT to each other."
+          ' Hold error message in a string array.
+          arErrors(nArraySlot) = strErrorMsg
+          ' Increment array slot counter.
+          nArraySlot = nArraySlot + 1
+        End If
+      End If
+    End If
+    ' 3) Determine if timekeeper initial is selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TKPR_INIT, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TKPR_NAME, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Both timekeeper name and initial are selected.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "Both the Timekeeper Initials and Timekeeper Name was selected. Only ONE of the items can be selected."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+    ' 4) Determine if timekeeper rank is selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_RANK, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Timekeeper rank is selected, thus check if timekeeper name or initial is also selected.
+      nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TKPR_INIT, sCOLUMN_TITLE_TO_SEARCH)
+      nItemPosition3 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_TKPR_NAME, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition2 = 0 And nItemPosition3 = 0) Then
+        ' No timekeeper name or initial selected.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Rank was selected but no Timekeeper Initials or Timekeeper Name was selected. The Timekeeper Initials or Timekeeper Name MUST be selected with the Rank."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If 
+    End If
+    ' 5) Determine if phase and task are selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_CLNT_PHASE, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_CLNT_TASK, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Phase and task are selected, check if the task is after the phase.
+      If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) ) Then
+        ' Task is not directly to right of Phase.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Task MUST be IMMEDIATELY AFTER the Phase."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 6) Determine if task and activity code are selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_CLNT_TASK, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_ACTIVITY, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Task and activity code are selected, check if activity code is after task.
+      If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) ) Then
+        ' Activity is not directly to right of Task.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Activity Code MUST be IMMEDIATELY AFTER the Task."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 7) Determine if narrative has been selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_NARRATIVE, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 = 0) Then
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Narrative MUST be selected and located in position " + CStr(sLIST_ITEM_TIME_NARRATIVE_LOC_1) + " or " + CStr(sLIST_ITEM_TIME_NARRATIVE_LOC_2) + " as it is a MANDATORY item."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    Else
+      ' Narrative selected, determine if its located in position 2 or 3.
+      If (nItemPosition1 &lt;&gt; sLIST_ITEM_TIME_NARRATIVE_LOC_1 And nItemPosition1 &lt;&gt; sLIST_ITEM_TIME_NARRATIVE_LOC_2) Then
+        ' Narrative not in position. 
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Narrative MUST be located in position " + CStr(sLIST_ITEM_TIME_NARRATIVE_LOC_1) + " or " + CStr(sLIST_ITEM_TIME_NARRATIVE_LOC_2) + "."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 8) Determine if billed amount is selected.
+    nItemPosition1 = FindListItem(hDestinationListTD, sLIST_ITEM_TIME_BILL_AMT, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition1 &lt;&gt; hDestinationListTD.Count) Then
+      ' Billed amount is selected and is not located in the last position.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Billed Amount MUST be selected in the LAST position."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+    ' 9) Determine if selected items has exceeded maximum allow.
+    If (hDestinationListTD.Count &gt; nMAX_ITEMS) Then
+      ' Selected items.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The number of items selected has exceeded the maximum number (" + CStr(nMAX_ITEMS) + ") allowed."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+  End If  ' Time Detail Flag Check.
+  ' DISBURSEMENT SUMMARY
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_DS_INCLDE").Value = hField("_HSF_CHK_DS_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    ' 1) Determine if timekeeper name is selected.
+    nItemPosition1 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_TKPR_NAME, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Timekeeper name is selected.
+      ' Determine if the timekeeper code is selected.
+      nItemPosition2 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_TKPR_CODE, sCOLUMN_TITLE_TO_SEARCH)
+      If (nItemPosition2 &gt; 0) Then
+        ' Timekeeper code is selected, check if the code is close to the timekeeper name.
+        If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) And (nItemPosition2 &lt;&gt; (nItemPosition1 - 1) And nItemPosition1 &gt; 1 ) ) Then
+          ' Timekeeper code and name are not next to each other.
+          nErrorCount = nErrorCount + 1
+          strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Timekeeper Code and Timekeeper Name MUST be selected NEXT to each other."
+          ' Hold error message in a string array.
+          arErrors(nArraySlot) = strErrorMsg
+          ' Increment array slot counter.
+          nArraySlot = nArraySlot + 1
+        End If
+      End If
+    End If
+    ' 2) Determine if disbursement description is selected.
+    nItemPosition1 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_COST_DESC, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 = 0) Then
+      ' Cost description not selected.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Disbursement Description MUST be selected as it is a MANDATORY item."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+    ' 3) Determine if disbursement code and disbursment description are selected.
+    nItemPosition1 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_COST_CODE, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_COST_DESC, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Disbursement group code and disbursement group description are selected.
+      ' Determine if the disbursement group code is before the disbursement group description.
+      If ( (nItemPosition1 &gt; nItemPosition2) Or (nItemPosition1 &lt;&gt; (nItemPosition2 - 1) And nItemPosition2 &gt; 1) ) Then
+        ' Disbursement group code is not before disbursement group description.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Disbursement Code MUST be IMMEDIATELY BEFORE the Disbursement Description."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 4) Determine if disbursement group code and disbursement group description are selected.
+    nItemPosition1 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_GROUP_CODE, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_GROUP_DESC, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Disbursement group code and disbursement group description are selected.
+      ' Determine if the disbursement group code is before the disbursement group description.
+      If ( (nItemPosition1 &gt; nItemPosition2) Or (nItemPosition1 &lt;&gt; (nItemPosition2 - 1) And nItemPosition2 &gt; 1) ) Then
+        ' Disbursement group code is not before disbursement group description.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Disbursement Group Code MUST be IMMEDIATELY BEFORE Disbursement Group Description."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 5) Determine if phase and task are selected.
+    nItemPosition1 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_CLNT_PHASE, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_CLNT_TASK, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Phase and task are selected, check if the task is after the phase.
+      If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) ) Then
+        ' Task is not directly to right of Phase.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Task MUST be IMMEDIATELY AFTER the Phase."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 6) Determine if billed amount is selected.
+    nItemPosition1 = FindListItem(hDestinationListDS, sLIST_ITEM_DISB_BILL_AMT, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0) Then
+      ' Billed amount is selected.
+      ' Determine if the billed amount is the last selected item.
+      If nItemPosition1 &lt;&gt; hDestinationListDS.Count Then
+        ' Billed amount not last item selected.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Amount MUST be selected in the LAST position."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    Else
+      ' Billed amount not selected.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The Amount MUST be selected as it is a MANDATORY item."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+    ' 7) Determine if selected items has exceeded maximum allow.
+    If (hDestinationListDS.Count &gt; nMAX_ITEMS) Then
+      ' Selected items.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_DISB_SUMMARY + ebTAB + "The number of items selected has exceeded the maximum number (" + CStr(nMAX_ITEMS) + ") allowed."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+  End If  ' Disbursement Summary Flag Check.
+  ' DISBURSEMENT DETAIL
+  ' Determine if value is ticked.
+  If hField("_HSF_CHK_DD_INCLDE").Value = hField("_HSF_CHK_DD_INCLDE").Checkbox.OnValue Then
+    ' Value is ticked.
+    ' 1) Determine if transaction date selected.
+    nItemPosition1 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_TRAN_DATE, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition1 &lt;&gt; 1) Then
+      ' Transaction date is selected but not in first position.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The Date MUST be selected in the FIRST position."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+    ' 2) Determine if timekeeper code and name are selected.
+    nItemPosition1 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_TKPR_NAME, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_TKPR_CODE, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Timekeeper code and name are selected, check if the code is close to the timekeeper name.
+      If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) And (nItemPosition2 &lt;&gt; (nItemPosition1 - 1) And nItemPosition1 &gt; 1 ) ) Then
+        ' Timekeeper code and name are not next to each other.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The Timekeeper Code and Timekeeper Name MUST be selected NEXT to each other."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 3) Determine if disbursement code and description are selected.
+    nItemPosition1 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_COST_CODE, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_COST_DESC, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Disbursement code and name are selected, check if the code is before description.
+      If ( (nItemPosition1 &gt; nItemPosition2) Or (nItemPosition1 &lt;&gt; (nItemPosition2 - 1) And nItemPosition2 &gt; 1) ) Then
+        ' Disbursement code is not before the disbursement description.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The Disbursement Code MUST be IMMEDIATELY BEFORE the Disbursement Description."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 4) Determine if task is selected.
+    nItemPosition1 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_CLNT_PHASE, sCOLUMN_TITLE_TO_SEARCH)
+    nItemPosition2 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_CLNT_TASK, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 &gt; 0 And nItemPosition2 &gt; 0) Then
+      ' Phase and task are selected, check if the task is after the phase.
+      If ( (nItemPosition2 &lt;&gt; (nItemPosition1 + 1) And nItemPosition1 &gt; 0) ) Then
+        ' Task is not directly to right of Phase.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_TIME_DETAIL + ebTAB + "The Task MUST be IMMEDIATELY AFTER the Phase."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 5) Determine if billed amount is selected.
+    nItemPosition1 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_BILL_AMT, sCOLUMN_TITLE_TO_SEARCH) 
+    If (nItemPosition1 &gt; 0) Then
+      ' Billed amount is selected.
+      ' Determine if the billed amount is the last selected item.
+      If nItemPosition1 &lt;&gt; hDestinationListDD.Count Then
+        ' Billed amount not last item selected.
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The Amount MUST be selected in the LAST position."
+        ' Hold error message in a string array.
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter.
+        nArraySlot = nArraySlot + 1
+      End If
+    End If
+    ' 6) Determine if narrative has been selected.
+    nItemPosition1 = FindListItem(hDestinationListDD, sLIST_ITEM_DISB_NARRATIVE, sCOLUMN_TITLE_TO_SEARCH)
+    If (nItemPosition1 = 0) Then
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The Narrative MUST be selected and located in position " + CStr(sLIST_ITEM_DISB_NARRATIVE_LOC_1) 
+      strErrorMsg = strErrorMsg + ", " + CStr(sLIST_ITEM_DISB_NARRATIVE_LOC_2) + " or " + CStr(sLIST_ITEM_DISB_NARRATIVE_LOC_3) + "  as it is a MANDATORY item."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    Else
+      ' Narrative selected, determine if its located in position 1, 2 or 3.
+      If (nItemPosition1 &lt;&gt; sLIST_ITEM_DISB_NARRATIVE_LOC_1 And nItemPosition1 &lt;&gt; sLIST_ITEM_DISB_NARRATIVE_LOC_2 And nItemPosition1 &lt;&gt; sLIST_ITEM_DISB_NARRATIVE_LOC_3) Then
+        ' Narrative not in position. 
+        ' Increment error counter.
+        nErrorCount = nErrorCount + 1
+        strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The Narrative MUST be located in position " + CStr(sLIST_ITEM_DISB_NARRATIVE_LOC_1)
+        strErrorMsg = strErrorMsg + ", " + CStr(sLIST_ITEM_DISB_NARRATIVE_LOC_2) + " or " + CStr(sLIST_ITEM_DISB_NARRATIVE_LOC_3) + "."
+        ' Hold error message in a string array. 
+        arErrors(nArraySlot) = strErrorMsg
+        ' Increment array slot counter. 
+        nArraySlot = nArraySlot + 1 
+      End If
+    End If
+    ' 7) Determine if selected items has exceeded maximum allow.
+    If (hDestinationListDD.Count &gt; nMAX_ITEMS) Then
+      ' Selected items.
+      ' Increment error counter.
+      nErrorCount = nErrorCount + 1
+      strErrorMsg = sSECTION_DISB_DETAIL + ebTAB + "The number of items selected has exceeded the maximum number (" + CStr(nMAX_ITEMS) + ") allowed."
+      ' Hold error message in a string array.
+      arErrors(nArraySlot) = strErrorMsg
+      ' Increment array slot counter.
+      nArraySlot = nArraySlot + 1
+    End If
+  End If  ' Disbursement Detail Flag Check.
+  ' DISPLAY ERROR MESSAGE
+  ' Determine if there are any errors.
+  If nErrorCount &gt; 0 Then
+    Dim nArrayNum As Long
+    nArrayNum = UBound(arErrors)
+    ' Determine if any elements in Error array.
+    If UBound(arErrors) &gt; 0 Then
+      ' There are errors, display them.
+      hForm.LoadSubForm sOPTION_VALIDATION_ERROR_SCREEN
+      For nLoop = 0 To UBound(arErrors) - 1
+        ' Determine if line is non blank.      
+        If Trim$(arErrors(nLoop)) &lt;&gt; "" Then
+          hForm.Form.Fields("_LIST").List.AddRow arErrors(nLoop)
+        End If
+      Next nLoop
+      hForm.WaitForClose
+    End If ' Array Entries,
+    ValidateRecord = FALSE
+  Else
+    ValidateRecord = TRUE
+  End If
+  ' Reset handles.
+  Set hField = Nothing
+  Set hDestinationListTS = Nothing
+  Set hDestinationListTD = Nothing
+  Set hDestinationListDS = Nothing
+  Set hDestinationListDD = Nothing
+  Set hForm = Nothing
+End Function
+Sub ModeChange(nMode As Integer)
+  Dim hField As Fields
+  ' Obtain object handle.
+  Set hField = ThisField.Form.Fields
+  If nMode = MODE_CHANGE Then
+    ' Determine if value is ticked.
+    If hField("_HSF_CHK_GN_DT_RNG").Value = hField("_HSF_CHK_GN_DT_RNG").Checkbox.OnValue Then
+      ' Value is ticked.
+      ' Value is not ticked.
+      hField("_HSF_RB_GN_DT_OPT").Enabled = TRUE
+    Else
+      ' Value is not ticked.
+      hField("_HSF_RB_GN_DT_OPT").Enabled = FALSE
+    End If
+  End If
+  ' Determine if include matter cost to date is ticked.
+  If hField("_HSF_CHK_GN_INC_MC").Value = hField("_HSF_CHK_GN_INC_MC").Checkbox.OnValue Then
+    ' Value is ticked.
+    hField("_HSF_RB_GN_MC_OP").Enabled = TRUE
+  Else
+    ' Value is not ticked.
+    hField("_HSF_RB_GN_MC_OP").Enabled = FALSE
+  End If
+  If gbAccessDiscount Then
+    hField("_HSF_GN_PCT_DISC").Enabled = TRUE
+  Else
+    hField("_HSF_GN_PCT_DISC").Enabled = FALSE
+  End If
+'  InfoMessage "nMode = " + CStr(nMode)
+  ' Release object handle.
+  Set hField = Nothing
+End Sub
+Sub Load()
+  Const sFROM_CLIENT As String = "TBMCLNT"
+  Const sFROM_MATTER As String = "TBMMATT3"
+  Const sCMD_START_PARM As String = "START"
+  Const sSECTION_GENERAL As String = "GN"
+  Const sSECTION_COVER_LETTER As String = "CL"
+  Const sSECTION_TIME_SUMMARY As String = "TS"
+  Const sSECTION_TIME_DETAIL As String = "TD"
+  Const sSECTION_DISB_SUMMARY As String = "DS"
+  Const sSECTION_DISB_DETAIL As String = "DD"
+  Const sSECTION_DISB_DETAIL_DISB_ONLY As String = "DDDI"
+  Const sWG_REFERENCE_INVOICE_OPTION_FULL As String = "CMRF"
+  Const sWG_CLIENT_MATTER_EDIT As String = "CMED"
+  Dim strMsg As String
+  Dim strClientCode As String
+  Dim strClientName As String
+  Dim strMatterCode As String
+  Dim strMatterName As String
+  Dim strCode As String
+  Dim hListTSAvail As List
+  Dim hListTSIncl As List
+  Dim hListTDAvail As List
+  Dim hListTDIncl As List
+  Dim hListDSAvail As List
+  Dim hListDSIncl As List
+  Dim hListDDAvail As List
+  Dim hListDDIncl As List
+  Dim hListDDDisbAvail As List
+  Dim hListDDDisbIncl As List
+  Dim f As Fields
+  ' Obtain object handle.
+  Set f = ThisField.Form.Fields
+  Set hListTSAvail = f("_HSF_LST_TS_AVAIL").List
+  Set hListTSIncl = f("_HSF_LST_TS_INCL").List
+  Set hListTDAvail = f("_HSF_LST_TD_AVAIL").List
+  Set hListTDIncl = f("_HSF_LST_TD_INCL").List
+  Set hListDSAvail = f("_HSF_LST_DS_AVAIL").List
+  Set hListDSIncl = f("_HSF_LST_DS_INCL").List
+  Set hListDDAvail = f("_HSF_LST_DD_AVAIL").List
+  Set hListDDIncl = f("_HSF_LST_DD_INCL").List
+  Set hListDDDisbAvail = f("_HSF_LST_DD_DI_AVL").List
+  Set hListDDDisbIncl = f("_HSF_LST_DD_DI_INC").List
+  ' Obtain the first commandline value.
+  gstrCmdExe = CStr(CommandLine.Value(sCMD_START_PARM))
+  ' Display the General information.
+  Call SectionArea(f, sSECTION_GENERAL)
+  ' Initialise variables.
+  strClientCode = ""
+  strClientName = ""
+  strMatterCode = ""
+  strMatterName = ""
+  ' Determine where the screen is launched from and set the header information.
+  If gstrCmdExe = sFROM_CLIENT Then
+    strClientCode = ThisField.ParentForm.Fields("CLIENT_CODE").Value
+    strClientName = ThisField.ParentForm.Fields("CLIENT_NAME").Value
+    strMatterCode = ""
+    strMatterName = ""
+    f("_HSF_CLIENT_CODE").Value = strClientCode
+    f("_HSF_CLIENT_NAME").Value = strClientName
+    f("_HSF_MATTER_CODE").Value = strMatterCode
+    f("_HSF_MATTER_NAME").Value = strMatterName
+  ElseIf gstrCmdExe = sFROM_MATTER Then
+    strClientCode = ThisField.ParentForm.Fields("CLIENT_CODE").Value
+    strClientName = ThisField.ParentForm.Fields("CLIENT_NAME").Value
+    strMatterCode = ThisField.ParentForm.Fields("MATTER_CODE").Value
+    strMatterName = ThisField.ParentForm.Fields("MATTER_NAME").Value
+    f("_HSF_CLIENT_CODE").Value = strClientCode
+    f("_HSF_CLIENT_NAME").Value = strClientName
+    f("_HSF_MATTER_CODE").Value = strMatterCode
+    f("_HSF_MATTER_NAME").Value = strMatterName
+  Else
+    f("_HSF_CLIENT_CODE").Value = gstrClientCode
+    f("_HSF_CLIENT_NAME").Value = gstrClientName
+    f("_HSF_MATTER_CODE").Value = gstrMatterCode
+    f("_HSF_MATTER_NAME").Value = gstrMatterName
+  End If
+  ' Load Time Summary lists.
+  strCode = f("_HSF_TS_LIST_ITEM").Value
+  Call LoadAvailable(hListTSAvail, sSECTION_TIME_SUMMARY, strCode)
+  Call LoadSelected(hListTSIncl, sSECTION_TIME_SUMMARY, strCode)
+  ' Load Time Detail lists.
+  strCode = f("_HSF_TD_LIST_ITEM").Value
+  Call LoadAvailable(hListTDAvail, sSECTION_TIME_DETAIL, strCode)
+  Call LoadSelected(hListTDIncl, sSECTION_TIME_DETAIL, strCode)
+  ' Load Disbursement Summary lists.
+  strCode = f("_HSF_DS_LIST_ITEM").Value
+  Call LoadAvailable(hListDSAvail, sSECTION_DISB_SUMMARY, strCode)
+  Call LoadSelected(hListDSIncl, sSECTION_DISB_SUMMARY, strCode)
+  ' Load Disbursement Detail lists.
+  strCode = f("_HSF_DD_LIST_ITEM").Value
+  Call LoadAvailable(hListDDAvail, sSECTION_DISB_DETAIL, strCode)
+  Call LoadSelected(hListDDIncl, sSECTION_DISB_DETAIL, strCode)
+  ' Disbursement codes
+  strCode = f("_HSF_DD_LIST_DISB").Value
+  Call LoadAvailable(hListDDDisbAvail, sSECTION_DISB_DETAIL_DISB_ONLY, strCode)
+  Call LoadSelected(hListDDDisbIncl, sSECTION_DISB_DETAIL_DISB_ONLY, strCode)
+  Dim hSQL As New SQLAccess
+  Dim strSQL As String
+  Dim strResult as string
+  strSQL = "SELECT TOP 1 ISNULL("
+  strSQL = strSQL + " (SELECT 1 ALLOWED FROM dbo.HBM_PERSNL WHERE PRIVILEGE_LEVEL=1 AND EMPL_UNO =(" + CStr(UserInfo.EMPL_UNO) + ")"
+  strSQL = strSQL + " UNION "
+  strSQL = strSQL + " SELECT 1 ALLOWED FROM dbo.HBA_PERSNL_WKGP A "
+  strSQL = strSQL + " JOIN dbo.HBL_WORK_GROUP B ON B.WORK_GROUP_UNO = A.WORK_GROUP_UNO "
+  strSQL = strSQL + " WHERE B.WORK_GROUP_CODE IN ('CMRF','CMED') "
+  strSQL = strSQL + " AND A.EMPL_UNO = (" + CStr(UserInfo.EMPL_UNO) + ")"
+  strSQL = strSQL + " ),0) ALLOWED "
+  strSQL = strSQL + " ORDER BY 1 DESC "
+  ' Execute SQL statement.
+  hSQL.IssueCommand strSQL
+  strResult = Trim$(hSQL.Value("ALLOWED"))
+    ' Determine if user is in specified workgroup or Privilege Level 1.
+  If strResult = "1" Then
+    gbAccessDiscount = TRUE
+  Else
+    gbAccessDiscount = FALSE
+  End If
+  If gbAccessDiscount Then
+    f("_HSF_GN_PCT_DISC").Enabled = TRUE
+  Else
+    f("_HSF_GN_PCT_DISC").Enabled = FALSE
+  End If
+  ' Release object handle.
+  Set f = Nothing
+  Set hListTSAvail = Nothing
+  Set hListTSIncl = Nothing
+  Set hListTDAvail = Nothing
+  Set hListTDIncl = Nothing
+  Set hListDSAvail = Nothing
+  Set hListDSIncl = Nothing
+  Set hListDDAvail = Nothing
+  Set hListDDIncl = Nothing
+  Set hListDDDisbAvail = Nothing
+  Set hListDDDisbIncl = Nothing
+End Sub
+</t>
   </si>
   <si>
     <t>CMSEdit</t>
@@ -1435,9 +3060,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="9">
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
@@ -1445,8 +3074,36 @@
       <sz val="24"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Consolas"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1456,6 +3113,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB7093"/>
       </patternFill>
     </fill>
   </fills>
@@ -1468,29 +3130,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" applyFont="1" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" applyFont="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" applyFont="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1502,1488 +3175,1503 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.892942428588867" customWidth="1"/>
-    <col min="2" max="2" width="24.4791202545166" customWidth="1"/>
-    <col min="3" max="3" width="66.17457580566406" customWidth="1"/>
-    <col min="4" max="4" width="54.205474853515625" customWidth="1"/>
+    <col min="1" max="1" width="32.107887268066406" customWidth="1"/>
+    <col min="2" max="2" width="34.5807991027832" customWidth="1"/>
+    <col min="3" max="3" width="96.25392150878906" customWidth="1"/>
+    <col min="4" max="4" width="78.84432220458984" customWidth="1"/>
     <col min="5" max="5" width="300" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="3" customFormat="1">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
+      <c r="B3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="8" t="s">
         <v>45</v>
       </c>
+      <c r="E12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="5" t="s">
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="B32" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="D32" s="8"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="B43" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="6"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="A44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="6"/>
+      <c r="C44" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="9"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="A45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="6"/>
+      <c r="C45" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="9"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="A46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="C46" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>45</v>
-      </c>
+      <c r="D46" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E46" s="9"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="A47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="C47" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="6"/>
+      <c r="D47" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="5" t="s">
+      <c r="A48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="6"/>
+      <c r="C48" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="9"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="6"/>
+      <c r="A49" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="9"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="A50" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E50" s="6"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="6"/>
+      <c r="A51" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E51" s="9"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="6"/>
+      <c r="A52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="6"/>
+      <c r="A53" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="6"/>
+      <c r="A54" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="9"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="6"/>
+      <c r="A55" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="9"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E56" s="6"/>
+      <c r="A56" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="9"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57" s="6"/>
+      <c r="A57" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="9"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E58" s="6"/>
+      <c r="A58" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="9"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D59" s="5" t="s">
+      <c r="A59" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E59" s="6"/>
+      <c r="C59" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E59" s="9"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="A60" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E60" s="6"/>
+      <c r="C60" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="9"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C61" s="5" t="s">
+      <c r="A61" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="6" t="s">
+      <c r="C61" s="8" t="s">
         <v>170</v>
       </c>
+      <c r="D61" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E61" s="9"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="B62" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="6" t="s">
+      <c r="C62" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="9" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="A63" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="6" t="s">
+      <c r="C63" s="8" t="s">
         <v>176</v>
       </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="9" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="A64" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="6" t="s">
+      <c r="C64" s="8" t="s">
         <v>179</v>
       </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="9" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="A65" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="6" t="s">
+      <c r="C65" s="8" t="s">
         <v>182</v>
       </c>
+      <c r="D65" s="8"/>
+      <c r="E65" s="9" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="A66" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="6" t="s">
+      <c r="C66" s="8" t="s">
         <v>185</v>
       </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="9" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="A67" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="6" t="s">
+      <c r="C67" s="8" t="s">
         <v>188</v>
       </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="9" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="A68" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D68" s="5"/>
-      <c r="E68" s="6" t="s">
+      <c r="C68" s="8" t="s">
         <v>191</v>
       </c>
+      <c r="D68" s="8"/>
+      <c r="E68" s="9" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="A69" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D69" s="5"/>
-      <c r="E69" s="6" t="s">
+      <c r="C69" s="8" t="s">
         <v>194</v>
       </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="9" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" s="5"/>
-      <c r="E70" s="6" t="s">
+      <c r="A70" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>196</v>
       </c>
+      <c r="C70" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" s="9" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B71" s="5" t="s">
+      <c r="A71" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="6" t="s">
-        <v>198</v>
+      <c r="D71" s="8"/>
+      <c r="E71" s="9" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="6" t="s">
-        <v>200</v>
+      <c r="A72" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" s="9" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D73" s="5"/>
-      <c r="E73" s="6" t="s">
+      <c r="A73" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>203</v>
       </c>
+      <c r="C73" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" s="9" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D74" s="5"/>
-      <c r="E74" s="6" t="s">
+      <c r="A74" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>205</v>
       </c>
+      <c r="C74" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D74" s="8"/>
+      <c r="E74" s="9" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B75" s="5" t="s">
+      <c r="A75" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="6" t="s">
-        <v>207</v>
+      <c r="D75" s="8"/>
+      <c r="E75" s="9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="6" t="s">
-        <v>209</v>
+      <c r="A76" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="9" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D77" s="5"/>
-      <c r="E77" s="6" t="s">
-        <v>211</v>
+      <c r="A77" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" s="9" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D78" s="5"/>
-      <c r="E78" s="6" t="s">
-        <v>213</v>
+      <c r="A78" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D78" s="8"/>
+      <c r="E78" s="9" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="6" t="s">
-        <v>45</v>
+      <c r="A79" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="6"/>
+      <c r="A80" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="6"/>
+      <c r="A81" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="9"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="6"/>
+      <c r="A82" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="9"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C83" s="5" t="s">
+      <c r="A83" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D83" s="5"/>
-      <c r="E83" s="6"/>
+      <c r="B83" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="9"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C84" s="5" t="s">
+      <c r="A84" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="9"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="9"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="6"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B85" s="5" t="s">
+      <c r="B86" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" s="9"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" s="9"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="6"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B86" s="5" t="s">
+      <c r="B88" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="6"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C87" s="5" t="s">
+      <c r="D88" s="8"/>
+      <c r="E88" s="9"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="9"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="6"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C88" s="5" t="s">
+      <c r="B90" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" s="9"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="6"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="6"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="6"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D91" s="5"/>
-      <c r="E91" s="6"/>
+      <c r="B91" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="9"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D92" s="5"/>
-      <c r="E92" s="6"/>
+      <c r="A92" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" s="9"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C93" s="5" t="s">
+      <c r="A93" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" s="9"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="9"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="9"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="6"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="6"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="6"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D97" s="5"/>
-      <c r="E97" s="6"/>
+      <c r="A97" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D97" s="8"/>
+      <c r="E97" s="9"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D98" s="5"/>
-      <c r="E98" s="6"/>
+      <c r="A98" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D98" s="8"/>
+      <c r="E98" s="9"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="6"/>
+      <c r="A99" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="9"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C100" s="5" t="s">
+      <c r="A100" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D100" s="5"/>
-      <c r="E100" s="6"/>
+      <c r="B100" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" s="9"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="6"/>
+      <c r="A101" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="9"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="9"/>
     </row>
   </sheetData>
   <headerFooter/>
